--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260715.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260715.xlsx
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>致伸</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>53,345,000</t>
+          <t>16,825,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>26,770,000</t>
+          <t>53,345,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>12,994,000</t>
+          <t>26,770,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>致伸</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>16,825,000</t>
+          <t>12,994,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>新產</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>5,564,000</t>
+          <t>7,850,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>新產</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>7,850,000</t>
+          <t>5,564,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>國產</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>24,248,000</t>
+          <t>7,825,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>國產</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>7,825,000</t>
+          <t>24,248,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
